--- a/Upwork_Templates/Land_Business/Land_Business.xlsx
+++ b/Upwork_Templates/Land_Business/Land_Business.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Upwork_Templates\Land_Business\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BBBBCCA-8E15-4391-8E6B-45AA9695524C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A9D336-EC32-4F18-8E47-08B604C318A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E78915C1-152E-40B2-92CA-ABB34D326D02}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{E78915C1-152E-40B2-92CA-ABB34D326D02}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="description" sheetId="2" r:id="rId2"/>
+    <sheet name="Input" sheetId="1" r:id="rId1"/>
+    <sheet name="Summary" sheetId="3" r:id="rId2"/>
+    <sheet name="description" sheetId="2" r:id="rId3"/>
+    <sheet name="Monthly" sheetId="5" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,6 +39,56 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>SMS Sent</t>
+  </si>
+  <si>
+    <t>Leads</t>
+  </si>
+  <si>
+    <t>Avg. Response Time</t>
+  </si>
+  <si>
+    <t>Total Leads</t>
+  </si>
+  <si>
+    <t>Deals</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>ROI</t>
+  </si>
+  <si>
+    <t>ROAS</t>
+  </si>
+  <si>
+    <t>Cost/Lead</t>
+  </si>
+  <si>
+    <t>Cost/Deal</t>
+  </si>
+  <si>
+    <t>Revenue/Deal</t>
+  </si>
+  <si>
+    <t>ART</t>
+  </si>
+  <si>
+    <t>Q1. What is the meaning of Total Lead? Is it the SUM of all leads from the starting date, if it so, should I go on adding infinitely as the data is added in Input Tab.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
@@ -55,7 +108,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -63,12 +116,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1445,6 +1515,108 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDF78A75-E1A1-456F-BA1B-BC8576C01864}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23DBC854-5FE1-4C00-8D6E-D70C019834D1}">
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E19550-698B-44E4-B38F-38D32CF2F600}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BADCA3F-993D-4F4D-81D0-D79CD6E0AAFE}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -1452,12 +1624,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1E19550-698B-44E4-B38F-38D32CF2F600}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E09A01E3-8C94-4E81-8B45-622BAE5E86BF}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>